--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
   <si>
     <t/>
   </si>
@@ -737,12 +737,6 @@
   </si>
   <si>
     <t>SAMYANG ROSE 140G</t>
-  </si>
-  <si>
-    <t>20139701</t>
-  </si>
-  <si>
-    <t>SAMYANG S.CURRY 140G</t>
   </si>
   <si>
     <t>20135130</t>
@@ -1474,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3656,10 +3650,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3667,19 +3661,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3696,10 +3690,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3716,10 +3710,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3736,10 +3730,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3756,10 +3750,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -3776,10 +3770,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -3796,10 +3790,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3807,19 +3801,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3836,10 +3830,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
@@ -3856,10 +3850,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>19</v>
@@ -3876,13 +3870,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3896,10 +3890,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3907,22 +3901,22 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3936,10 +3930,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>169</v>
@@ -3956,13 +3950,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3976,13 +3970,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3996,10 +3990,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>19</v>
@@ -4016,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4036,10 +4030,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4047,19 +4041,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4076,10 +4070,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4096,10 +4090,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4116,10 +4110,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>19</v>
@@ -4136,13 +4130,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4156,10 +4150,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>169</v>
@@ -4176,10 +4170,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>169</v>
@@ -4196,30 +4190,30 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4236,10 +4230,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>19</v>
@@ -4256,10 +4250,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>19</v>
@@ -4276,30 +4270,30 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4316,10 +4310,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4336,10 +4330,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4356,10 +4350,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4376,10 +4370,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4396,10 +4390,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4416,10 +4410,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4427,19 +4421,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4456,10 +4450,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4476,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4496,10 +4490,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4516,10 +4510,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4527,19 +4521,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4556,10 +4550,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4576,10 +4570,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>6</v>
@@ -4596,30 +4590,30 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>6</v>
+        <v>194</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>194</v>
@@ -4636,10 +4630,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>194</v>
@@ -4656,13 +4650,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4676,32 +4670,12 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F161" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="353">
   <si>
     <t/>
   </si>
@@ -52,192 +52,198 @@
     <t>6</t>
   </si>
   <si>
+    <t>20062365</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 A/KRM133</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20084444</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 A.KCP129</t>
+  </si>
+  <si>
+    <t>20124567</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 A.GPK126</t>
+  </si>
+  <si>
+    <t>20129436</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 RDANG132</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20138877</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 ACEH 140</t>
+  </si>
+  <si>
+    <t>10007606</t>
+  </si>
+  <si>
+    <t>ABC MIE GULAI PDS.70</t>
+  </si>
+  <si>
     <t>20141070</t>
   </si>
   <si>
     <t>KOBE MI CH/OIL LV.15</t>
   </si>
   <si>
+    <t>20131022</t>
+  </si>
+  <si>
+    <t>SDAAP MIE GRG BKED87</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
+  </si>
+  <si>
+    <t>20096590</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 5'S</t>
+  </si>
+  <si>
+    <t>20140674</t>
+  </si>
+  <si>
+    <t>SEDAAP AYM BWG 5'S</t>
+  </si>
+  <si>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM BWG70</t>
+  </si>
+  <si>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
+  </si>
+  <si>
+    <t>10023791</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KR.AYAM72</t>
+  </si>
+  <si>
+    <t>20025418</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KARI SP75</t>
+  </si>
+  <si>
+    <t>20049556</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM KR 88</t>
+  </si>
+  <si>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>20114755</t>
+  </si>
+  <si>
+    <t>SDP MIE SPC.LAKSA 83</t>
+  </si>
+  <si>
+    <t>20125555</t>
+  </si>
+  <si>
+    <t>SEDAP MI KRN CH/BL86</t>
+  </si>
+  <si>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
+  </si>
+  <si>
+    <t>20131690</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM JRT77</t>
+  </si>
+  <si>
+    <t>20123024</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO.MDR82</t>
+  </si>
+  <si>
+    <t>20099679</t>
+  </si>
+  <si>
+    <t>LEMONILO MIE GRG 65G</t>
+  </si>
+  <si>
+    <t>20099678</t>
+  </si>
+  <si>
+    <t>LEMONILO AYM BWG 60G</t>
+  </si>
+  <si>
+    <t>20113972</t>
+  </si>
+  <si>
+    <t>LEMONILO PDS KOREA68</t>
+  </si>
+  <si>
+    <t>20132986</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI TRYKI120</t>
+  </si>
+  <si>
+    <t>20094693</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI AYM 5.5K</t>
+  </si>
+  <si>
+    <t>20119164</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI YKNKU115</t>
+  </si>
+  <si>
+    <t>20135313</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI BOLOG76</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>20062365</t>
-  </si>
-  <si>
-    <t>SUKSES ISI2 A/KRM133</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20084444</t>
-  </si>
-  <si>
-    <t>SUKSES ISI2 A.KCP129</t>
-  </si>
-  <si>
-    <t>20124567</t>
-  </si>
-  <si>
-    <t>SUKSES ISI2 A.GPK126</t>
-  </si>
-  <si>
-    <t>20129436</t>
-  </si>
-  <si>
-    <t>SUKSES ISI2 RDANG132</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20138877</t>
-  </si>
-  <si>
-    <t>SUKSES ISI2 ACEH 140</t>
-  </si>
-  <si>
-    <t>20131022</t>
-  </si>
-  <si>
-    <t>SDAAP MIE GRG BKED87</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
-  </si>
-  <si>
-    <t>20096590</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 5'S</t>
-  </si>
-  <si>
-    <t>20140674</t>
-  </si>
-  <si>
-    <t>SEDAAP AYM BWG 5'S</t>
-  </si>
-  <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM BWG70</t>
-  </si>
-  <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
-  </si>
-  <si>
-    <t>10023791</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KR.AYAM72</t>
-  </si>
-  <si>
-    <t>20025418</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KARI SP75</t>
-  </si>
-  <si>
-    <t>20049556</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM KR 88</t>
-  </si>
-  <si>
-    <t>20136385</t>
-  </si>
-  <si>
-    <t>SEDAAP GRG CHF.DVN93</t>
-  </si>
-  <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>20114755</t>
-  </si>
-  <si>
-    <t>SDP MIE SPC.LAKSA 83</t>
-  </si>
-  <si>
-    <t>20125555</t>
-  </si>
-  <si>
-    <t>SEDAP MI KRN CH/BL86</t>
-  </si>
-  <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
-  </si>
-  <si>
-    <t>20131690</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM JRT77</t>
-  </si>
-  <si>
-    <t>20123024</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO.MDR82</t>
-  </si>
-  <si>
-    <t>20099679</t>
-  </si>
-  <si>
-    <t>LEMONILO MIE GRG 65G</t>
-  </si>
-  <si>
-    <t>20099678</t>
-  </si>
-  <si>
-    <t>LEMONILO AYM BWG 60G</t>
-  </si>
-  <si>
-    <t>20113972</t>
-  </si>
-  <si>
-    <t>LEMONILO PDS KOREA68</t>
-  </si>
-  <si>
-    <t>20132986</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI TRYKI120</t>
-  </si>
-  <si>
-    <t>20094693</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI AYM 5.5K</t>
-  </si>
-  <si>
-    <t>20119164</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI YKNKU115</t>
-  </si>
-  <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI BOLOG76</t>
-  </si>
-  <si>
     <t>20135312</t>
   </si>
   <si>
@@ -274,21 +280,15 @@
     <t>INDOMIE AYAM BWG 5S</t>
   </si>
   <si>
-    <t>10007606</t>
-  </si>
-  <si>
-    <t>ABC MIE GULAI PDS.70</t>
+    <t>10003435</t>
+  </si>
+  <si>
+    <t>SUPERMI AYAM BWG 75G</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>10003435</t>
-  </si>
-  <si>
-    <t>SUPERMI AYAM BWG 75G</t>
-  </si>
-  <si>
     <t>10015954</t>
   </si>
   <si>
@@ -301,6 +301,12 @@
     <t>GAGA 100 GR.JLPNO 85</t>
   </si>
   <si>
+    <t>10000713</t>
+  </si>
+  <si>
+    <t>INDOMI KLD AYAM 75G</t>
+  </si>
+  <si>
     <t>10002560</t>
   </si>
   <si>
@@ -343,61 +349,76 @@
     <t>10</t>
   </si>
   <si>
-    <t>10000713</t>
-  </si>
-  <si>
-    <t>INDOMI KLD AYAM 75G</t>
-  </si>
-  <si>
     <t>10000652</t>
   </si>
   <si>
     <t>INDOMI AYAM BWNG 69G</t>
   </si>
   <si>
+    <t>10000184</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM SPECL68G</t>
+  </si>
+  <si>
+    <t>10035954</t>
+  </si>
+  <si>
+    <t>INDOMIE EMPL/GTNG 75</t>
+  </si>
+  <si>
+    <t>10035955</t>
+  </si>
+  <si>
+    <t>INDOMIE MI KOCOK 75G</t>
+  </si>
+  <si>
+    <t>20085115</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG ACEH 90G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20044199</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG CB.IJO85</t>
+  </si>
+  <si>
+    <t>20074112</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RICA 85G</t>
+  </si>
+  <si>
+    <t>20138358</t>
+  </si>
+  <si>
+    <t>INDOMI NYEMK B/LDS80</t>
+  </si>
+  <si>
+    <t>20140632</t>
+  </si>
+  <si>
+    <t>INDOMI NYMEK J/RD 84</t>
+  </si>
+  <si>
     <t>20133372</t>
   </si>
   <si>
     <t>INDOMIE RWN MERCON75</t>
   </si>
   <si>
-    <t>10035954</t>
-  </si>
-  <si>
-    <t>INDOMIE EMPL/GTNG 75</t>
-  </si>
-  <si>
-    <t>10035955</t>
-  </si>
-  <si>
-    <t>INDOMIE MI KOCOK 75G</t>
-  </si>
-  <si>
-    <t>10000184</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM SPECL68G</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACEH 90G</t>
-  </si>
-  <si>
-    <t>20044199</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG CB.IJO85</t>
-  </si>
-  <si>
-    <t>20074112</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RICA 85G</t>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>20019930</t>
@@ -406,27 +427,6 @@
     <t>INDOMIE GRG RNDANG91</t>
   </si>
   <si>
-    <t>20138358</t>
-  </si>
-  <si>
-    <t>INDOMI NYEMK B/LDS80</t>
-  </si>
-  <si>
-    <t>20140632</t>
-  </si>
-  <si>
-    <t>INDOMI NYMEK J/RD 84</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>20128381</t>
   </si>
   <si>
@@ -535,6 +535,12 @@
     <t>3AYAM MIE TLR KNG200</t>
   </si>
   <si>
+    <t>10037027</t>
+  </si>
+  <si>
+    <t>AAA BIHUN 220GR</t>
+  </si>
+  <si>
     <t>20043409</t>
   </si>
   <si>
@@ -550,12 +556,6 @@
     <t>BIHUN JAGUNG 320G</t>
   </si>
   <si>
-    <t>10037027</t>
-  </si>
-  <si>
-    <t>AAA BIHUN 220GR</t>
-  </si>
-  <si>
     <t>20140909</t>
   </si>
   <si>
@@ -572,12 +572,6 @@
   </si>
   <si>
     <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20132768</t>
-  </si>
-  <si>
-    <t>OMOIDE KAKE UDON 215</t>
   </si>
   <si>
     <t>10000245</t>
@@ -1468,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1570,73 +1564,73 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1650,41 +1644,41 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1693,18 +1687,18 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1713,18 +1707,18 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1733,18 +1727,18 @@
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1753,158 +1747,158 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1913,18 +1907,18 @@
         <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1933,18 +1927,18 @@
         <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1953,18 +1947,18 @@
         <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1973,18 +1967,18 @@
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1993,38 +1987,38 @@
         <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2033,18 +2027,18 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2053,18 +2047,18 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2073,18 +2067,18 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2093,18 +2087,18 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -2113,50 +2107,50 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2170,13 +2164,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2190,13 +2184,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,10 +2204,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2230,10 +2224,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2250,10 +2244,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2270,30 +2264,30 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2310,10 +2304,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2330,10 +2324,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2350,10 +2344,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2361,19 +2355,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2390,10 +2384,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2410,10 +2404,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2430,10 +2424,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2450,10 +2444,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2461,19 +2455,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2490,10 +2484,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2510,10 +2504,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2530,10 +2524,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2550,10 +2544,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2593,7 +2587,7 @@
         <v>122</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2633,7 +2627,7 @@
         <v>122</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2690,10 +2684,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -2701,19 +2695,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -2753,7 +2747,7 @@
         <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2793,7 +2787,7 @@
         <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2853,7 +2847,7 @@
         <v>140</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2893,7 +2887,7 @@
         <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -2933,7 +2927,7 @@
         <v>155</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -2976,7 +2970,7 @@
         <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2993,7 +2987,7 @@
         <v>166</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>169</v>
@@ -3033,7 +3027,7 @@
         <v>166</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -3056,15 +3050,15 @@
         <v>9</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3076,7 +3070,7 @@
         <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>6</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3093,10 +3087,10 @@
         <v>166</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3116,7 +3110,7 @@
         <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3150,53 +3144,53 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3210,13 +3204,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3230,13 +3224,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3250,13 +3244,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3270,13 +3264,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3290,33 +3284,33 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3330,13 +3324,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3350,13 +3344,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3370,13 +3364,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3390,13 +3384,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3410,13 +3404,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3430,33 +3424,33 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3470,13 +3464,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3490,13 +3484,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3510,13 +3504,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3530,33 +3524,33 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3570,13 +3564,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3590,10 +3584,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -3610,13 +3604,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3630,33 +3624,33 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3670,13 +3664,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3690,13 +3684,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3710,13 +3704,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3730,13 +3724,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3750,13 +3744,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3770,33 +3764,33 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3810,13 +3804,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3830,13 +3824,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3850,13 +3844,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3870,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3881,22 +3875,22 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3910,10 +3904,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>169</v>
@@ -3930,13 +3924,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3950,13 +3944,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3970,13 +3964,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3990,13 +3984,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4010,33 +4004,33 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4050,13 +4044,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4070,13 +4064,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4090,13 +4084,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4110,13 +4104,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4130,10 +4124,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>169</v>
@@ -4150,10 +4144,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>169</v>
@@ -4170,33 +4164,33 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4210,13 +4204,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4230,13 +4224,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4250,30 +4244,30 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -4290,10 +4284,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4310,10 +4304,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4330,10 +4324,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4350,10 +4344,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4370,10 +4364,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4390,10 +4384,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4401,19 +4395,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4430,10 +4424,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4450,10 +4444,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4470,7 +4464,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>9</v>
@@ -4490,10 +4484,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4501,19 +4495,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4530,10 +4524,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4550,10 +4544,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4570,33 +4564,33 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4610,13 +4604,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4630,13 +4624,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4650,33 +4644,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
   <si>
     <t/>
   </si>
@@ -503,6 +503,12 @@
   </si>
   <si>
     <t>INDOMIE GRG RNDNG120</t>
+  </si>
+  <si>
+    <t>20142599</t>
+  </si>
+  <si>
+    <t>INDOMI GR CB.IJO 120</t>
   </si>
   <si>
     <t>20085013</t>
@@ -1462,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2964,53 +2970,53 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3024,10 +3030,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -3044,13 +3050,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3064,33 +3070,33 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3104,93 +3110,93 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3204,13 +3210,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3224,13 +3230,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3244,13 +3250,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3264,13 +3270,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3284,10 +3290,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>16</v>
@@ -3295,19 +3301,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>16</v>
@@ -3324,10 +3330,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>16</v>
@@ -3344,13 +3350,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3364,13 +3370,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3384,10 +3390,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>16</v>
@@ -3404,13 +3410,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3424,30 +3430,30 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>16</v>
@@ -3464,10 +3470,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>16</v>
@@ -3484,10 +3490,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>16</v>
@@ -3504,10 +3510,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>16</v>
@@ -3524,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>16</v>
@@ -3535,19 +3541,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>16</v>
@@ -3564,13 +3570,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3584,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -3604,13 +3610,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3624,10 +3630,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>16</v>
@@ -3635,19 +3641,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>16</v>
@@ -3664,10 +3670,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>16</v>
@@ -3684,10 +3690,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>16</v>
@@ -3704,10 +3710,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>16</v>
@@ -3724,10 +3730,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>16</v>
@@ -3744,10 +3750,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>16</v>
@@ -3764,10 +3770,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>16</v>
@@ -3775,19 +3781,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>16</v>
@@ -3804,10 +3810,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>16</v>
@@ -3824,10 +3830,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>16</v>
@@ -3844,13 +3850,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3864,10 +3870,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3875,22 +3881,22 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3904,13 +3910,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3924,13 +3930,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3944,13 +3950,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3964,10 +3970,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>16</v>
@@ -3984,10 +3990,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>16</v>
@@ -4004,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>16</v>
@@ -4015,19 +4021,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>16</v>
@@ -4044,10 +4050,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>16</v>
@@ -4064,10 +4070,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>16</v>
@@ -4084,10 +4090,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>16</v>
@@ -4104,13 +4110,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4124,13 +4130,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4144,13 +4150,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4164,30 +4170,30 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>16</v>
@@ -4204,10 +4210,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>16</v>
@@ -4224,10 +4230,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>16</v>
@@ -4244,30 +4250,30 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -4284,10 +4290,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4304,10 +4310,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4324,10 +4330,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4344,10 +4350,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4364,10 +4370,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4384,10 +4390,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4395,19 +4401,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4424,10 +4430,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4444,10 +4450,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4464,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4484,10 +4490,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4495,19 +4501,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4524,10 +4530,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4544,10 +4550,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4564,33 +4570,33 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4604,13 +4610,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4624,13 +4630,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4644,12 +4650,32 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E159" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F159" s="1" t="s">
+      <c r="F160" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -988,7 +988,7 @@
     <t>20091304</t>
   </si>
   <si>
-    <t>POP MIE PD.GLD AYM75</t>
+    <t>P/MIE GRG P.GLD AY75</t>
   </si>
   <si>
     <t>27</t>
@@ -997,7 +997,7 @@
     <t>20084481</t>
   </si>
   <si>
-    <t>POP MIE PD.DWR AYM75</t>
+    <t>P/MIE P.DWR SQDAYM75</t>
   </si>
   <si>
     <t>20131530</t>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -703,7 +703,7 @@
     <t>20129224</t>
   </si>
   <si>
-    <t>MJGAE SPCY RPKI 260G</t>
+    <t>MJGAE SPCY RPKI 155G</t>
   </si>
   <si>
     <t>20096499</t>
@@ -775,13 +775,13 @@
     <t>20141466</t>
   </si>
   <si>
-    <t>RMNYES TKYO CHKN 84G</t>
+    <t>RMN YES TKYO CHKN84G</t>
   </si>
   <si>
     <t>20141464</t>
   </si>
   <si>
-    <t>RMNYES HKTA CHKN 88G</t>
+    <t>RMN YES HKTA CHKN88G</t>
   </si>
   <si>
     <t>20039494</t>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -97,529 +97,568 @@
     <t>ABC MIE GULAI PDS.70</t>
   </si>
   <si>
+    <t>20131022</t>
+  </si>
+  <si>
+    <t>SDAAP MIE GRG BKED87</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
+  </si>
+  <si>
+    <t>20096590</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 5'S</t>
+  </si>
+  <si>
+    <t>20140674</t>
+  </si>
+  <si>
+    <t>SEDAAP AYM BWG 5'S</t>
+  </si>
+  <si>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM BWG70</t>
+  </si>
+  <si>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
+  </si>
+  <si>
+    <t>10023791</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KR.AYAM72</t>
+  </si>
+  <si>
+    <t>20025418</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KARI SP75</t>
+  </si>
+  <si>
+    <t>20049556</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM KR 88</t>
+  </si>
+  <si>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>20114755</t>
+  </si>
+  <si>
+    <t>SDP MIE SPC.LAKSA 83</t>
+  </si>
+  <si>
+    <t>20125555</t>
+  </si>
+  <si>
+    <t>SEDAP MI KRN CH/BL86</t>
+  </si>
+  <si>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
+  </si>
+  <si>
+    <t>20131690</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM JRT77</t>
+  </si>
+  <si>
+    <t>20123024</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO.MDR82</t>
+  </si>
+  <si>
+    <t>20099679</t>
+  </si>
+  <si>
+    <t>LEMONILO MIE GRG 65G</t>
+  </si>
+  <si>
+    <t>20099678</t>
+  </si>
+  <si>
+    <t>LEMONILO AYM BWG 60G</t>
+  </si>
+  <si>
+    <t>20113972</t>
+  </si>
+  <si>
+    <t>LEMONILO PDS KOREA68</t>
+  </si>
+  <si>
+    <t>20132986</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI TRYKI120</t>
+  </si>
+  <si>
+    <t>20094693</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI AYM 5.5K</t>
+  </si>
+  <si>
+    <t>20119164</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI YKNKU115</t>
+  </si>
+  <si>
+    <t>20135313</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI BOLOG76</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI CARB80</t>
+  </si>
+  <si>
+    <t>20137860</t>
+  </si>
+  <si>
+    <t>WOW AGLI OLIO 75G</t>
+  </si>
+  <si>
+    <t>20138738</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI CRBO 80G</t>
+  </si>
+  <si>
+    <t>20138739</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI BGLN 84G</t>
+  </si>
+  <si>
+    <t>20140633</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG SPC 5S</t>
+  </si>
+  <si>
+    <t>20140657</t>
+  </si>
+  <si>
+    <t>INDOMIE AYAM BWG 5S</t>
+  </si>
+  <si>
+    <t>10003435</t>
+  </si>
+  <si>
+    <t>SUPERMI AYAM BWG 75G</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10015954</t>
+  </si>
+  <si>
+    <t>GAGA 100 JALAPENO 75</t>
+  </si>
+  <si>
+    <t>20085444</t>
+  </si>
+  <si>
+    <t>GAGA 100 GR.JLPNO 85</t>
+  </si>
+  <si>
+    <t>10000713</t>
+  </si>
+  <si>
+    <t>INDOMI KLD AYAM 75G</t>
+  </si>
+  <si>
+    <t>10002560</t>
+  </si>
+  <si>
+    <t>INDOMI SOTO MIE 70GR</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20007834</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO SPCL 75</t>
+  </si>
+  <si>
+    <t>20085462</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO LMNG 80</t>
+  </si>
+  <si>
+    <t>20137101</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO PD.D 76</t>
+  </si>
+  <si>
+    <t>20137102</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO KN 76G</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10000652</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM BWNG 69G</t>
+  </si>
+  <si>
+    <t>10000184</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM SPECL68G</t>
+  </si>
+  <si>
+    <t>10035954</t>
+  </si>
+  <si>
+    <t>INDOMIE EMPL/GTNG 75</t>
+  </si>
+  <si>
+    <t>10035955</t>
+  </si>
+  <si>
+    <t>INDOMIE MI KOCOK 75G</t>
+  </si>
+  <si>
+    <t>20085115</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG ACEH 90G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20074112</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RICA 85G</t>
+  </si>
+  <si>
+    <t>20044199</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG CB.IJO85</t>
+  </si>
+  <si>
+    <t>20138358</t>
+  </si>
+  <si>
+    <t>INDOMI NYEMK B/LDS80</t>
+  </si>
+  <si>
+    <t>20140632</t>
+  </si>
+  <si>
+    <t>INDOMI NYMEK J/RD 84</t>
+  </si>
+  <si>
+    <t>20133372</t>
+  </si>
+  <si>
+    <t>INDOMIE RWN MERCON75</t>
+  </si>
+  <si>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20019930</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDANG91</t>
+  </si>
+  <si>
+    <t>20128381</t>
+  </si>
+  <si>
+    <t>INDOMI TRI MSO RMN86</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20132338</t>
+  </si>
+  <si>
+    <t>INDOMIE TORI KARA 89</t>
+  </si>
+  <si>
+    <t>20135989</t>
+  </si>
+  <si>
+    <t>INDOMI SPCY RMYEON83</t>
+  </si>
+  <si>
+    <t>20135990</t>
+  </si>
+  <si>
+    <t>INDOMI FIERY CHKIN94</t>
+  </si>
+  <si>
+    <t>20136533</t>
+  </si>
+  <si>
+    <t>INDOMIE K-ROSE 85G</t>
+  </si>
+  <si>
+    <t>20101747</t>
+  </si>
+  <si>
+    <t>INDOMI SBLAK HOT/J75</t>
+  </si>
+  <si>
+    <t>20093221</t>
+  </si>
+  <si>
+    <t>INDOMIE GR AYM.GP 85</t>
+  </si>
+  <si>
+    <t>20032100</t>
+  </si>
+  <si>
+    <t>INDOMIE KRT/AYM PG90</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20032099</t>
+  </si>
+  <si>
+    <t>INDOMIE KRT/GR.SPC90</t>
+  </si>
+  <si>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR SP JUMB129</t>
+  </si>
+  <si>
+    <t>10003801</t>
+  </si>
+  <si>
+    <t>INDOMI JMB AYM PG127</t>
+  </si>
+  <si>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDNG120</t>
+  </si>
+  <si>
+    <t>20142599</t>
+  </si>
+  <si>
+    <t>INDOMI GR CB.IJO 120</t>
+  </si>
+  <si>
+    <t>20085013</t>
+  </si>
+  <si>
+    <t>BD MIE URAI ORG 140G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>10000507</t>
+  </si>
+  <si>
+    <t>A/B MIE TELOR 200GR</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004055</t>
+  </si>
+  <si>
+    <t>3AYAM MIE TLR MRH200</t>
+  </si>
+  <si>
+    <t>10004262</t>
+  </si>
+  <si>
+    <t>3AYAM MIE TLR KNG200</t>
+  </si>
+  <si>
+    <t>10037027</t>
+  </si>
+  <si>
+    <t>AAA BIHUN 220GR</t>
+  </si>
+  <si>
+    <t>20043409</t>
+  </si>
+  <si>
+    <t>IDM BIHUN BERAS 220G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20034699</t>
+  </si>
+  <si>
+    <t>BIHUN JAGUNG 320G</t>
+  </si>
+  <si>
+    <t>10000245</t>
+  </si>
+  <si>
+    <t>RATU ABON SAPI 90G</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20140909</t>
+  </si>
+  <si>
+    <t>B.FARM TERI KB 60G</t>
+  </si>
+  <si>
+    <t>20020770</t>
+  </si>
+  <si>
+    <t>MERBABU KR.BAWANG200</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138950</t>
+  </si>
+  <si>
+    <t>IDM ABON AYAM 80G</t>
+  </si>
+  <si>
+    <t>20112822</t>
+  </si>
+  <si>
+    <t>MIGELAS AYAM BWG 6'S</t>
+  </si>
+  <si>
+    <t>20094642</t>
+  </si>
+  <si>
+    <t>MIGELAS SOTO AYAM 6S</t>
+  </si>
+  <si>
+    <t>20032996</t>
+  </si>
+  <si>
+    <t>PALDO HOT&amp;SPICY 120</t>
+  </si>
+  <si>
+    <t>20138114</t>
+  </si>
+  <si>
+    <t>PALDO BIBMEN II 130G</t>
+  </si>
+  <si>
+    <t>20127764</t>
+  </si>
+  <si>
+    <t>N/SHIM STIR FRY 131</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20138271</t>
+  </si>
+  <si>
+    <t>N/SHIM STR CHESE 136</t>
+  </si>
+  <si>
+    <t>20138170</t>
+  </si>
+  <si>
+    <t>N/SHIM SPCY CHK 120G</t>
+  </si>
+  <si>
+    <t>20141816</t>
+  </si>
+  <si>
+    <t>N/SHIM TOOMBA 137GR</t>
+  </si>
+  <si>
     <t>20141070</t>
   </si>
   <si>
     <t>KOBE MI CH/OIL LV.15</t>
   </si>
   <si>
-    <t>20131022</t>
-  </si>
-  <si>
-    <t>SDAAP MIE GRG BKED87</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
-  </si>
-  <si>
-    <t>20096590</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 5'S</t>
-  </si>
-  <si>
-    <t>20140674</t>
-  </si>
-  <si>
-    <t>SEDAAP AYM BWG 5'S</t>
-  </si>
-  <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM BWG70</t>
-  </si>
-  <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
-  </si>
-  <si>
-    <t>10023791</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KR.AYAM72</t>
-  </si>
-  <si>
-    <t>20025418</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KARI SP75</t>
-  </si>
-  <si>
-    <t>20049556</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM KR 88</t>
-  </si>
-  <si>
-    <t>20136385</t>
-  </si>
-  <si>
-    <t>SEDAAP GRG CHF.DVN93</t>
-  </si>
-  <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>20114755</t>
-  </si>
-  <si>
-    <t>SDP MIE SPC.LAKSA 83</t>
-  </si>
-  <si>
-    <t>20125555</t>
-  </si>
-  <si>
-    <t>SEDAP MI KRN CH/BL86</t>
-  </si>
-  <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
-  </si>
-  <si>
-    <t>20131690</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM JRT77</t>
-  </si>
-  <si>
-    <t>20123024</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO.MDR82</t>
-  </si>
-  <si>
-    <t>20099679</t>
-  </si>
-  <si>
-    <t>LEMONILO MIE GRG 65G</t>
-  </si>
-  <si>
-    <t>20099678</t>
-  </si>
-  <si>
-    <t>LEMONILO AYM BWG 60G</t>
-  </si>
-  <si>
-    <t>20113972</t>
-  </si>
-  <si>
-    <t>LEMONILO PDS KOREA68</t>
-  </si>
-  <si>
-    <t>20132986</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI TRYKI120</t>
-  </si>
-  <si>
-    <t>20094693</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI AYM 5.5K</t>
-  </si>
-  <si>
-    <t>20119164</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI YKNKU115</t>
-  </si>
-  <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI BOLOG76</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI CARB80</t>
-  </si>
-  <si>
-    <t>20137860</t>
-  </si>
-  <si>
-    <t>WOW AGLI OLIO 75G</t>
-  </si>
-  <si>
-    <t>20138738</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI CRBO 80G</t>
-  </si>
-  <si>
-    <t>20138739</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI BGLN 84G</t>
-  </si>
-  <si>
-    <t>20140633</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG SPC 5S</t>
-  </si>
-  <si>
-    <t>20140657</t>
-  </si>
-  <si>
-    <t>INDOMIE AYAM BWG 5S</t>
-  </si>
-  <si>
-    <t>10003435</t>
-  </si>
-  <si>
-    <t>SUPERMI AYAM BWG 75G</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10015954</t>
-  </si>
-  <si>
-    <t>GAGA 100 JALAPENO 75</t>
-  </si>
-  <si>
-    <t>20085444</t>
-  </si>
-  <si>
-    <t>GAGA 100 GR.JLPNO 85</t>
-  </si>
-  <si>
-    <t>10000713</t>
-  </si>
-  <si>
-    <t>INDOMI KLD AYAM 75G</t>
-  </si>
-  <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20007834</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO SPCL 75</t>
-  </si>
-  <si>
-    <t>20085462</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO LMNG 80</t>
-  </si>
-  <si>
-    <t>20137101</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO PD.D 76</t>
-  </si>
-  <si>
-    <t>20137102</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO KN 76G</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10000652</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM BWNG 69G</t>
-  </si>
-  <si>
-    <t>10000184</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM SPECL68G</t>
-  </si>
-  <si>
-    <t>10035954</t>
-  </si>
-  <si>
-    <t>INDOMIE EMPL/GTNG 75</t>
-  </si>
-  <si>
-    <t>10035955</t>
-  </si>
-  <si>
-    <t>INDOMIE MI KOCOK 75G</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACEH 90G</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20044199</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG CB.IJO85</t>
-  </si>
-  <si>
-    <t>20074112</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RICA 85G</t>
-  </si>
-  <si>
-    <t>20138358</t>
-  </si>
-  <si>
-    <t>INDOMI NYEMK B/LDS80</t>
-  </si>
-  <si>
-    <t>20140632</t>
-  </si>
-  <si>
-    <t>INDOMI NYMEK J/RD 84</t>
-  </si>
-  <si>
-    <t>20133372</t>
-  </si>
-  <si>
-    <t>INDOMIE RWN MERCON75</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDANG91</t>
-  </si>
-  <si>
-    <t>20128381</t>
-  </si>
-  <si>
-    <t>INDOMI TRI MSO RMN86</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20132338</t>
-  </si>
-  <si>
-    <t>INDOMIE TORI KARA 89</t>
-  </si>
-  <si>
-    <t>20135989</t>
-  </si>
-  <si>
-    <t>INDOMI SPCY RMYEON83</t>
-  </si>
-  <si>
-    <t>20135990</t>
-  </si>
-  <si>
-    <t>INDOMI FIERY CHKIN94</t>
-  </si>
-  <si>
-    <t>20136533</t>
-  </si>
-  <si>
-    <t>INDOMIE K-ROSE 85G</t>
-  </si>
-  <si>
-    <t>20101747</t>
-  </si>
-  <si>
-    <t>INDOMI SBLAK HOT/J75</t>
-  </si>
-  <si>
-    <t>20093221</t>
-  </si>
-  <si>
-    <t>INDOMIE GR AYM.GP 85</t>
-  </si>
-  <si>
-    <t>20032100</t>
-  </si>
-  <si>
-    <t>INDOMIE KRT/AYM PG90</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20032099</t>
-  </si>
-  <si>
-    <t>INDOMIE KRT/GR.SPC90</t>
-  </si>
-  <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
-  </si>
-  <si>
-    <t>10003801</t>
-  </si>
-  <si>
-    <t>INDOMI JMB AYM PG127</t>
-  </si>
-  <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
-  </si>
-  <si>
-    <t>20142599</t>
-  </si>
-  <si>
-    <t>INDOMI GR CB.IJO 120</t>
-  </si>
-  <si>
-    <t>20085013</t>
-  </si>
-  <si>
-    <t>BD MIE URAI ORG 140G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>10000507</t>
-  </si>
-  <si>
-    <t>A/B MIE TELOR 200GR</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004055</t>
-  </si>
-  <si>
-    <t>3AYAM MIE TLR MRH200</t>
-  </si>
-  <si>
-    <t>10004262</t>
-  </si>
-  <si>
-    <t>3AYAM MIE TLR KNG200</t>
-  </si>
-  <si>
-    <t>10037027</t>
-  </si>
-  <si>
-    <t>AAA BIHUN 220GR</t>
-  </si>
-  <si>
-    <t>20043409</t>
-  </si>
-  <si>
-    <t>IDM BIHUN BERAS 220G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20034699</t>
-  </si>
-  <si>
-    <t>BIHUN JAGUNG 320G</t>
-  </si>
-  <si>
-    <t>20140909</t>
-  </si>
-  <si>
-    <t>B.FARM TERI KB 60G</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20020770</t>
-  </si>
-  <si>
-    <t>MERBABU KR.BAWANG200</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10000245</t>
-  </si>
-  <si>
-    <t>RATU ABON SAPI 90G</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
-  </si>
-  <si>
-    <t>20112822</t>
-  </si>
-  <si>
-    <t>MIGELAS AYAM BWG 6'S</t>
-  </si>
-  <si>
-    <t>20094642</t>
-  </si>
-  <si>
-    <t>MIGELAS SOTO AYAM 6S</t>
-  </si>
-  <si>
-    <t>20032996</t>
-  </si>
-  <si>
-    <t>PALDO HOT&amp;SPICY 120</t>
+    <t>20128247</t>
+  </si>
+  <si>
+    <t>WNHAE FRIED ROSE 97G</t>
   </si>
   <si>
     <t>20141198</t>
@@ -628,37 +667,31 @@
     <t>WONHAE TPOKI CARB 80</t>
   </si>
   <si>
-    <t>20127764</t>
-  </si>
-  <si>
-    <t>N/SHIM STIR FRY 131</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20138271</t>
-  </si>
-  <si>
-    <t>N/SHIM STR CHESE 136</t>
-  </si>
-  <si>
-    <t>20138170</t>
-  </si>
-  <si>
-    <t>N/SHIM SPCY CHK 120G</t>
-  </si>
-  <si>
-    <t>20128247</t>
-  </si>
-  <si>
-    <t>WNHAE FRIED ROSE 97G</t>
-  </si>
-  <si>
-    <t>20141816</t>
-  </si>
-  <si>
-    <t>N/SHIM TOOMBA 137GR</t>
+    <t>20019479</t>
+  </si>
+  <si>
+    <t>N/SHIM SPCY MUSHR120</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20115156</t>
+  </si>
+  <si>
+    <t>MUJIGAE TOPOKKI 180G</t>
+  </si>
+  <si>
+    <t>20124335</t>
+  </si>
+  <si>
+    <t>MUJIGAE JJNGMYN 265G</t>
+  </si>
+  <si>
+    <t>20129224</t>
+  </si>
+  <si>
+    <t>MJGAE SPCY RPKI 155G</t>
   </si>
   <si>
     <t>20117989</t>
@@ -667,76 +700,43 @@
     <t>M/S TOPOKKI ORI 132G</t>
   </si>
   <si>
-    <t>20138114</t>
-  </si>
-  <si>
-    <t>PALDO BIBMEN II 130G</t>
+    <t>20096499</t>
+  </si>
+  <si>
+    <t>SMYANG AYM CRBO 130G</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20052583</t>
+  </si>
+  <si>
+    <t>SMYANG GR PDS AYM140</t>
+  </si>
+  <si>
+    <t>20127820</t>
+  </si>
+  <si>
+    <t>SMYANG CRM CBNARA140</t>
+  </si>
+  <si>
+    <t>20112749</t>
+  </si>
+  <si>
+    <t>SAMYANG SPICY 120G</t>
+  </si>
+  <si>
+    <t>20138572</t>
+  </si>
+  <si>
+    <t>SAMYANG ROSE 140G</t>
   </si>
   <si>
     <t>20139702</t>
   </si>
   <si>
     <t>SMYANG QTR.CHSE 145G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20019479</t>
-  </si>
-  <si>
-    <t>N/SHIM SPCY MUSHR120</t>
-  </si>
-  <si>
-    <t>20115156</t>
-  </si>
-  <si>
-    <t>MUJIGAE TOPOKKI 180G</t>
-  </si>
-  <si>
-    <t>20124335</t>
-  </si>
-  <si>
-    <t>MUJIGAE JJNGMYN 265G</t>
-  </si>
-  <si>
-    <t>20129224</t>
-  </si>
-  <si>
-    <t>MJGAE SPCY RPKI 155G</t>
-  </si>
-  <si>
-    <t>20096499</t>
-  </si>
-  <si>
-    <t>SMYANG AYM CRBO 130G</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20052583</t>
-  </si>
-  <si>
-    <t>SMYANG GR PDS AYM140</t>
-  </si>
-  <si>
-    <t>20127820</t>
-  </si>
-  <si>
-    <t>SMYANG CRM CBNARA140</t>
-  </si>
-  <si>
-    <t>20112749</t>
-  </si>
-  <si>
-    <t>SAMYANG SPICY 120G</t>
-  </si>
-  <si>
-    <t>20138572</t>
-  </si>
-  <si>
-    <t>SAMYANG ROSE 140G</t>
   </si>
   <si>
     <t>20135130</t>
@@ -1696,7 +1696,7 @@
         <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1770,10 +1770,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>16</v>
@@ -1793,7 +1793,7 @@
         <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>16</v>
@@ -1813,7 +1813,7 @@
         <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>16</v>
@@ -1833,7 +1833,7 @@
         <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>16</v>
@@ -1853,7 +1853,7 @@
         <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>16</v>
@@ -1873,7 +1873,7 @@
         <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>16</v>
@@ -1890,10 +1890,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>16</v>
@@ -1913,7 +1913,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>16</v>
@@ -1933,7 +1933,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>16</v>
@@ -1953,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>16</v>
@@ -1973,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>16</v>
@@ -1993,7 +1993,7 @@
         <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>16</v>
@@ -2010,10 +2010,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>16</v>
@@ -2033,7 +2033,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>16</v>
@@ -2053,7 +2053,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>16</v>
@@ -2073,7 +2073,7 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>16</v>
@@ -2093,7 +2093,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>16</v>
@@ -2113,7 +2113,7 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>16</v>
@@ -2130,10 +2130,10 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>16</v>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>16</v>
@@ -2170,10 +2170,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>16</v>
@@ -2190,13 +2190,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,10 +2210,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2230,10 +2230,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2250,10 +2250,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2270,10 +2270,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2281,19 +2281,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2310,10 +2310,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2330,10 +2330,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2350,10 +2350,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2361,19 +2361,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2390,10 +2390,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2410,10 +2410,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2430,10 +2430,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2450,10 +2450,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2461,19 +2461,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2490,10 +2490,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2510,10 +2510,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2530,10 +2530,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2550,10 +2550,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2561,19 +2561,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2590,10 +2590,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2610,10 +2610,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2630,10 +2630,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2650,10 +2650,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -2670,10 +2670,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -2681,19 +2681,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -2710,10 +2710,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -2721,19 +2721,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -2750,10 +2750,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2770,10 +2770,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2790,10 +2790,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2810,10 +2810,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2830,10 +2830,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -2850,10 +2850,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2861,19 +2861,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -2890,10 +2890,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -2910,10 +2910,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -2930,10 +2930,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -2950,10 +2950,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>6</v>
@@ -2970,53 +2970,53 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3030,10 +3030,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -3050,13 +3050,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3070,33 +3070,33 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>180</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3110,10 +3110,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>6</v>
@@ -3121,19 +3121,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>16</v>
@@ -3150,10 +3150,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>188</v>
@@ -3176,15 +3176,15 @@
         <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3196,7 +3196,7 @@
         <v>15</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3216,7 +3216,7 @@
         <v>5</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3236,7 +3236,7 @@
         <v>23</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3256,7 +3256,7 @@
         <v>9</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3276,7 +3276,7 @@
         <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3290,10 +3290,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>16</v>
@@ -3301,19 +3301,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>16</v>
@@ -3330,10 +3330,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>16</v>
@@ -3350,10 +3350,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>16</v>
@@ -3370,10 +3370,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -3390,13 +3390,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3410,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>16</v>
@@ -3430,30 +3430,30 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>16</v>
@@ -3470,10 +3470,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>16</v>
@@ -3490,10 +3490,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>16</v>
@@ -3510,10 +3510,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>16</v>
@@ -3530,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>16</v>
@@ -3541,19 +3541,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>16</v>
@@ -3570,13 +3570,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3590,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -3610,13 +3610,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3630,10 +3630,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>16</v>
@@ -3753,7 +3753,7 @@
         <v>244</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>16</v>
@@ -3773,7 +3773,7 @@
         <v>244</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>16</v>
@@ -3916,7 +3916,7 @@
         <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3936,7 +3936,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4013,7 +4013,7 @@
         <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>16</v>
@@ -4136,7 +4136,7 @@
         <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4153,10 +4153,10 @@
         <v>285</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4173,10 +4173,10 @@
         <v>285</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4373,7 +4373,7 @@
         <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4393,7 +4393,7 @@
         <v>311</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4596,7 +4596,7 @@
         <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4616,7 +4616,7 @@
         <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4636,7 +4636,7 @@
         <v>5</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="353">
   <si>
     <t/>
   </si>
@@ -112,13 +112,13 @@
     <t>20096590</t>
   </si>
   <si>
-    <t>SEDAAP MIE SOTO 5'S</t>
+    <t>SEDAAP MI STO 5x76 G</t>
   </si>
   <si>
     <t>20140674</t>
   </si>
   <si>
-    <t>SEDAAP AYM BWG 5'S</t>
+    <t>SEDAAP MI AYB 5x71 G</t>
   </si>
   <si>
     <t>10023790</t>
@@ -682,12 +682,6 @@
     <t>MUJIGAE TOPOKKI 180G</t>
   </si>
   <si>
-    <t>20124335</t>
-  </si>
-  <si>
-    <t>MUJIGAE JJNGMYN 265G</t>
-  </si>
-  <si>
     <t>20129224</t>
   </si>
   <si>
@@ -703,7 +697,7 @@
     <t>20096499</t>
   </si>
   <si>
-    <t>SMYANG AYM CRBO 130G</t>
+    <t>SMYANG AYM CBO 130 G</t>
   </si>
   <si>
     <t>20</t>
@@ -1468,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3473,7 +3467,7 @@
         <v>220</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>16</v>
@@ -3493,7 +3487,7 @@
         <v>220</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>16</v>
@@ -3510,10 +3504,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>16</v>
@@ -3521,19 +3515,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>16</v>
@@ -3550,13 +3544,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3570,10 +3564,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -3590,13 +3584,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3610,10 +3604,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>16</v>
@@ -3630,10 +3624,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>16</v>
@@ -3641,19 +3635,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>16</v>
@@ -3670,10 +3664,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>16</v>
@@ -3690,10 +3684,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>16</v>
@@ -3710,10 +3704,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>16</v>
@@ -3730,10 +3724,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>16</v>
@@ -3750,10 +3744,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>16</v>
@@ -3770,10 +3764,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>16</v>
@@ -3781,19 +3775,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>16</v>
@@ -3810,10 +3804,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>16</v>
@@ -3830,10 +3824,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>16</v>
@@ -3850,13 +3844,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3870,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3881,22 +3875,22 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3910,10 +3904,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>169</v>
@@ -3930,13 +3924,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3950,13 +3944,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3970,10 +3964,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>16</v>
@@ -3990,10 +3984,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>16</v>
@@ -4010,10 +4004,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>16</v>
@@ -4021,19 +4015,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>16</v>
@@ -4050,10 +4044,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>16</v>
@@ -4070,10 +4064,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>16</v>
@@ -4090,10 +4084,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>16</v>
@@ -4110,13 +4104,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4130,10 +4124,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>169</v>
@@ -4150,10 +4144,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>169</v>
@@ -4170,30 +4164,30 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>16</v>
@@ -4210,10 +4204,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>16</v>
@@ -4230,10 +4224,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>16</v>
@@ -4250,30 +4244,30 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -4290,10 +4284,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4310,10 +4304,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4330,10 +4324,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4350,10 +4344,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4370,10 +4364,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4390,10 +4384,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4401,19 +4395,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4430,10 +4424,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4450,10 +4444,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4470,10 +4464,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4490,10 +4484,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4501,19 +4495,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4530,10 +4524,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4550,10 +4544,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4570,30 +4564,30 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>192</v>
@@ -4610,10 +4604,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>192</v>
@@ -4630,13 +4624,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4650,32 +4644,12 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F160" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -112,13 +112,13 @@
     <t>20096590</t>
   </si>
   <si>
-    <t>SEDAAP MI STO 5x76 G</t>
+    <t>SEDAAP MIE SOTO 5'S</t>
   </si>
   <si>
     <t>20140674</t>
   </si>
   <si>
-    <t>SEDAAP MI AYB 5x71 G</t>
+    <t>SEDAAP AYM BWG 5'S</t>
   </si>
   <si>
     <t>10023790</t>
@@ -697,7 +697,7 @@
     <t>20096499</t>
   </si>
   <si>
-    <t>SMYANG AYM CBO 130 G</t>
+    <t>SMYANG AYM CRBO 130G</t>
   </si>
   <si>
     <t>20</t>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="351">
   <si>
     <t/>
   </si>
@@ -197,12 +197,6 @@
   </si>
   <si>
     <t>LEMONILO MIE GRG 65G</t>
-  </si>
-  <si>
-    <t>20099678</t>
-  </si>
-  <si>
-    <t>LEMONILO AYM BWG 60G</t>
   </si>
   <si>
     <t>20113972</t>
@@ -1462,7 +1456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2027,7 +2021,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>16</v>
@@ -2047,7 +2041,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>16</v>
@@ -2067,7 +2061,7 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>16</v>
@@ -2087,7 +2081,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>16</v>
@@ -2104,10 +2098,10 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>16</v>
@@ -2115,19 +2109,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>16</v>
@@ -2144,10 +2138,10 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>16</v>
@@ -2164,13 +2158,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2184,10 +2178,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -2204,10 +2198,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2224,10 +2218,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2244,10 +2238,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2255,19 +2249,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2284,10 +2278,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2304,10 +2298,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2324,10 +2318,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2335,19 +2329,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2364,10 +2358,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2384,10 +2378,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2404,10 +2398,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2424,10 +2418,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2435,19 +2429,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2464,10 +2458,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2484,10 +2478,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2504,10 +2498,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2524,10 +2518,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2535,19 +2529,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2564,10 +2558,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2584,10 +2578,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2604,10 +2598,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2624,10 +2618,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2644,10 +2638,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -2655,19 +2649,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -2684,10 +2678,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -2695,19 +2689,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -2724,10 +2718,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -2744,10 +2738,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2764,10 +2758,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2784,10 +2778,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2804,10 +2798,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2824,10 +2818,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -2835,19 +2829,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2864,10 +2858,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -2884,10 +2878,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -2904,10 +2898,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -2924,10 +2918,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -2944,53 +2938,53 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>16</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3004,10 +2998,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>6</v>
@@ -3024,13 +3018,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3044,33 +3038,33 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>178</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3084,10 +3078,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>6</v>
@@ -3095,22 +3089,22 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3124,53 +3118,53 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="E85" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3184,13 +3178,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3204,13 +3198,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3224,13 +3218,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3244,13 +3238,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3264,30 +3258,30 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>16</v>
@@ -3304,10 +3298,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>16</v>
@@ -3324,10 +3318,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>16</v>
@@ -3344,13 +3338,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3364,10 +3358,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -3384,13 +3378,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3404,10 +3398,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>16</v>
@@ -3415,19 +3409,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>16</v>
@@ -3444,10 +3438,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>16</v>
@@ -3464,10 +3458,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>16</v>
@@ -3484,10 +3478,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>16</v>
@@ -3495,19 +3489,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>16</v>
@@ -3524,13 +3518,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3544,10 +3538,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3564,13 +3558,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3584,10 +3578,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>16</v>
@@ -3604,10 +3598,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>16</v>
@@ -3615,19 +3609,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>16</v>
@@ -3644,10 +3638,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>16</v>
@@ -3664,10 +3658,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>16</v>
@@ -3684,10 +3678,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>16</v>
@@ -3704,10 +3698,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>16</v>
@@ -3724,10 +3718,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>16</v>
@@ -3744,10 +3738,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>16</v>
@@ -3755,19 +3749,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>16</v>
@@ -3784,10 +3778,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>16</v>
@@ -3804,10 +3798,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>16</v>
@@ -3824,13 +3818,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3844,10 +3838,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -3855,22 +3849,22 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3884,13 +3878,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3904,13 +3898,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3924,13 +3918,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3944,10 +3938,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>16</v>
@@ -3964,10 +3958,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>16</v>
@@ -3984,10 +3978,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>16</v>
@@ -3995,19 +3989,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>16</v>
@@ -4024,10 +4018,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>16</v>
@@ -4044,10 +4038,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>16</v>
@@ -4064,10 +4058,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>16</v>
@@ -4084,13 +4078,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>16</v>
+        <v>167</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4104,13 +4098,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4124,13 +4118,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4144,30 +4138,30 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>16</v>
@@ -4184,10 +4178,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>16</v>
@@ -4204,10 +4198,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>16</v>
@@ -4224,30 +4218,30 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>6</v>
@@ -4264,10 +4258,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -4284,10 +4278,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4304,10 +4298,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4324,10 +4318,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4344,10 +4338,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4364,10 +4358,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4375,19 +4369,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4404,10 +4398,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4424,10 +4418,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4444,10 +4438,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4464,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4475,19 +4469,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4504,10 +4498,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4524,10 +4518,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4544,33 +4538,33 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>6</v>
+        <v>190</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4584,13 +4578,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4604,13 +4598,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4624,32 +4618,12 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F159" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="357">
   <si>
     <t/>
   </si>
@@ -52,6 +52,15 @@
     <t>6</t>
   </si>
   <si>
+    <t>20136020</t>
+  </si>
+  <si>
+    <t>SARIMI2 GR AYM.PD120</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20062365</t>
   </si>
   <si>
@@ -229,9 +238,6 @@
     <t>WOW SPAGHETI BOLOG76</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20135312</t>
   </si>
   <si>
@@ -865,6 +871,12 @@
     <t>SEDAAP MIE K/S CUP81</t>
   </si>
   <si>
+    <t>20130519</t>
+  </si>
+  <si>
+    <t>SDP MI AYM NMPOL 75G</t>
+  </si>
+  <si>
     <t>20113844</t>
   </si>
   <si>
@@ -1033,13 +1045,19 @@
     <t>POP MIE AYM BWG 75G</t>
   </si>
   <si>
+    <t>20055742</t>
+  </si>
+  <si>
+    <t>SMYANG GR PDS AYM105</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>20129840</t>
   </si>
   <si>
     <t>IDM MIE GRG INDO 88G</t>
-  </si>
-  <si>
-    <t>29</t>
   </si>
   <si>
     <t>20129841</t>
@@ -1456,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F161"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1558,73 +1576,73 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1638,41 +1656,41 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1681,18 +1699,18 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1701,18 +1719,18 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1721,18 +1739,18 @@
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1741,158 +1759,158 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1901,18 +1919,18 @@
         <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1921,18 +1939,18 @@
         <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1941,18 +1959,18 @@
         <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1961,18 +1979,18 @@
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1981,38 +1999,38 @@
         <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2021,18 +2039,18 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2041,18 +2059,18 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2061,18 +2079,18 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2081,30 +2099,30 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2118,13 +2136,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2138,13 +2156,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2158,13 +2176,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2178,10 +2196,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -2198,10 +2216,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2218,10 +2236,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2238,10 +2256,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2249,19 +2267,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2278,10 +2296,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2298,10 +2316,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2318,10 +2336,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2329,19 +2347,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2358,10 +2376,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2378,10 +2396,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2398,10 +2416,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2418,10 +2436,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2429,19 +2447,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2458,10 +2476,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2478,10 +2496,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2498,10 +2516,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2518,10 +2536,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2529,19 +2547,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2558,10 +2576,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2578,10 +2596,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2598,10 +2616,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2618,10 +2636,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2638,10 +2656,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -2649,19 +2667,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -2678,10 +2696,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -2689,19 +2707,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -2718,10 +2736,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -2738,10 +2756,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2758,10 +2776,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2778,10 +2796,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2798,10 +2816,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2818,10 +2836,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -2829,19 +2847,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2858,10 +2876,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -2878,10 +2896,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -2898,10 +2916,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -2918,10 +2936,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -2938,53 +2956,53 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2998,10 +3016,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>6</v>
@@ -3018,13 +3036,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3038,33 +3056,33 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3078,10 +3096,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>6</v>
@@ -3089,22 +3107,22 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3118,53 +3136,53 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>186</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="E85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3178,13 +3196,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3198,13 +3216,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3218,13 +3236,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3238,13 +3256,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,33 +3276,33 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,13 +3316,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3318,13 +3336,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3338,13 +3356,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3358,10 +3376,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -3378,13 +3396,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3398,33 +3416,33 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3438,13 +3456,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3458,13 +3476,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3478,33 +3496,33 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3518,13 +3536,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3538,10 +3556,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3558,13 +3576,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3578,13 +3596,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3598,33 +3616,33 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3638,13 +3656,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3658,13 +3676,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3678,13 +3696,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3698,13 +3716,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3718,13 +3736,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3738,33 +3756,33 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3778,13 +3796,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3798,13 +3816,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3818,13 +3836,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3838,10 +3856,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -3849,22 +3867,22 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3878,13 +3896,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3898,13 +3916,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,13 +3936,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3938,13 +3956,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3958,13 +3976,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3978,33 +3996,33 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4018,13 +4036,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4038,13 +4056,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4058,13 +4076,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4078,13 +4096,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4098,13 +4116,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4118,13 +4136,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4138,53 +4156,53 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4198,13 +4216,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4218,50 +4236,50 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -4278,10 +4296,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4298,10 +4316,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4318,10 +4336,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4338,10 +4356,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4358,10 +4376,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4369,19 +4387,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4389,19 +4407,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4418,10 +4436,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4438,10 +4456,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4458,10 +4476,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4469,19 +4487,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4489,19 +4507,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4518,10 +4536,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4538,53 +4556,53 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>190</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>190</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4598,13 +4616,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4618,13 +4636,73 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E158" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F158" s="1" t="s">
-        <v>16</v>
+      <c r="F160" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="359">
   <si>
     <t/>
   </si>
@@ -148,6 +148,12 @@
     <t>SEDAAP MIE KR.AYAM72</t>
   </si>
   <si>
+    <t>20131690</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM JRT77</t>
+  </si>
+  <si>
     <t>20025418</t>
   </si>
   <si>
@@ -190,12 +196,6 @@
     <t>SEDAAP MIE GORENG 91</t>
   </si>
   <si>
-    <t>20131690</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM JRT77</t>
-  </si>
-  <si>
     <t>20123024</t>
   </si>
   <si>
@@ -232,18 +232,24 @@
     <t>TASTY BAKMI YKNKU115</t>
   </si>
   <si>
+    <t>20143284</t>
+  </si>
+  <si>
+    <t>WOWSPAGETIGORENG79G</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI CARB80</t>
+  </si>
+  <si>
     <t>20135313</t>
   </si>
   <si>
     <t>WOW SPAGHETI BOLOG76</t>
   </si>
   <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI CARB80</t>
-  </si>
-  <si>
     <t>20137860</t>
   </si>
   <si>
@@ -274,15 +280,15 @@
     <t>INDOMIE AYAM BWG 5S</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>10003435</t>
   </si>
   <si>
     <t>SUPERMI AYAM BWG 75G</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>10015954</t>
   </si>
   <si>
@@ -556,15 +562,30 @@
     <t>BIHUN JAGUNG 320G</t>
   </si>
   <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138950</t>
+  </si>
+  <si>
+    <t>IDM ABON AYAM 80G</t>
+  </si>
+  <si>
     <t>10000245</t>
   </si>
   <si>
     <t>RATU ABON SAPI 90G</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>20140909</t>
   </si>
   <si>
@@ -580,30 +601,15 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
+    <t>20112822</t>
+  </si>
+  <si>
+    <t>MIGELAS AYAM BWG 6'S</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
-  </si>
-  <si>
-    <t>20112822</t>
-  </si>
-  <si>
-    <t>MIGELAS AYAM BWG 6'S</t>
-  </si>
-  <si>
     <t>20094642</t>
   </si>
   <si>
@@ -871,16 +877,16 @@
     <t>SEDAAP MIE K/S CUP81</t>
   </si>
   <si>
+    <t>20113844</t>
+  </si>
+  <si>
+    <t>SEDAAP MI AYM JRT 75</t>
+  </si>
+  <si>
     <t>20130519</t>
   </si>
   <si>
     <t>SDP MI AYM NMPOL 75G</t>
-  </si>
-  <si>
-    <t>20113844</t>
-  </si>
-  <si>
-    <t>SEDAAP MI AYM JRT 75</t>
   </si>
   <si>
     <t>20122255</t>
@@ -1474,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1916,10 +1922,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>19</v>
@@ -1939,7 +1945,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>19</v>
@@ -1959,7 +1965,7 @@
         <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>19</v>
@@ -1979,7 +1985,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>19</v>
@@ -1999,7 +2005,7 @@
         <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>19</v>
@@ -2019,7 +2025,7 @@
         <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>19</v>
@@ -2202,7 +2208,7 @@
         <v>26</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2276,10 +2282,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2299,7 +2305,7 @@
         <v>89</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2319,7 +2325,7 @@
         <v>89</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2339,7 +2345,7 @@
         <v>89</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2356,10 +2362,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2367,19 +2373,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2396,10 +2402,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2416,10 +2422,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2436,10 +2442,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2456,10 +2462,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2467,19 +2473,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2496,10 +2502,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2516,10 +2522,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2536,10 +2542,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2556,10 +2562,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2567,19 +2573,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2596,10 +2602,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2616,10 +2622,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2636,10 +2642,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2656,10 +2662,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -2676,10 +2682,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -2687,19 +2693,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -2716,10 +2722,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -2727,19 +2733,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -2756,10 +2762,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2776,10 +2782,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2796,10 +2802,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2816,10 +2822,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2836,10 +2842,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -2856,10 +2862,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2867,19 +2873,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -2896,10 +2902,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -2916,10 +2922,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -2936,10 +2942,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -2956,10 +2962,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>6</v>
@@ -2976,53 +2982,53 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3036,10 +3042,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -3056,13 +3062,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3076,33 +3082,33 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3116,10 +3122,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>6</v>
@@ -3127,42 +3133,42 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3176,73 +3182,73 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>192</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="C88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3256,13 +3262,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3276,13 +3282,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3296,30 +3302,30 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>19</v>
@@ -3336,10 +3342,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>19</v>
@@ -3356,10 +3362,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>19</v>
@@ -3376,13 +3382,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3396,10 +3402,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>6</v>
@@ -3416,13 +3422,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3436,10 +3442,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>19</v>
@@ -3447,19 +3453,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>19</v>
@@ -3476,10 +3482,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3496,10 +3502,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3516,10 +3522,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3527,19 +3533,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>19</v>
@@ -3556,13 +3562,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3576,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -3596,13 +3602,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3616,10 +3622,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>19</v>
@@ -3636,10 +3642,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>19</v>
@@ -3647,19 +3653,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3676,10 +3682,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3696,10 +3702,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3716,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3736,10 +3742,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3756,10 +3762,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -3776,10 +3782,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -3787,19 +3793,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3816,10 +3822,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3836,10 +3842,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
@@ -3856,13 +3862,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3876,10 +3882,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3887,22 +3893,22 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3916,13 +3922,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3936,13 +3942,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3956,13 +3962,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3976,10 +3982,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>19</v>
@@ -3996,10 +4002,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>19</v>
@@ -4016,10 +4022,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4027,19 +4033,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4056,10 +4062,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4076,10 +4082,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4096,10 +4102,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4116,10 +4122,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>19</v>
@@ -4136,13 +4142,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4156,13 +4162,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4176,13 +4182,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4196,30 +4202,30 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4236,10 +4242,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>19</v>
@@ -4256,10 +4262,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>19</v>
@@ -4276,30 +4282,30 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4316,10 +4322,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4336,10 +4342,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4356,10 +4362,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4376,10 +4382,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4396,10 +4402,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4416,10 +4422,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4427,19 +4433,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4456,10 +4462,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4476,10 +4482,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4496,10 +4502,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4516,10 +4522,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4527,19 +4533,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E153" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4556,10 +4562,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4576,10 +4582,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>6</v>
@@ -4596,33 +4602,33 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>192</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4636,13 +4642,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4656,13 +4662,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4676,13 +4682,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4696,12 +4702,32 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E161" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F161" s="1" t="s">
+      <c r="F162" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="363">
   <si>
     <t/>
   </si>
@@ -202,6 +202,432 @@
     <t>SEDAAP MIE STO.MDR82</t>
   </si>
   <si>
+    <t>20132986</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI TRYKI120</t>
+  </si>
+  <si>
+    <t>20094693</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI AYM 5.5K</t>
+  </si>
+  <si>
+    <t>20119164</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI YKNKU115</t>
+  </si>
+  <si>
+    <t>20140633</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG SPC 5S</t>
+  </si>
+  <si>
+    <t>20140657</t>
+  </si>
+  <si>
+    <t>INDOMIE AYAM BWG 5S</t>
+  </si>
+  <si>
+    <t>20143284</t>
+  </si>
+  <si>
+    <t>WOWSPAGETIGORENG79G</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI CARB80</t>
+  </si>
+  <si>
+    <t>20135313</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI BOLOG76</t>
+  </si>
+  <si>
+    <t>20137860</t>
+  </si>
+  <si>
+    <t>WOW AGLI OLIO 75G</t>
+  </si>
+  <si>
+    <t>20138738</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI CRBO 80G</t>
+  </si>
+  <si>
+    <t>20138739</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI BGLN 84G</t>
+  </si>
+  <si>
+    <t>20143393</t>
+  </si>
+  <si>
+    <t>I/P SPGT FR CKN CB80</t>
+  </si>
+  <si>
+    <t>20143392</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI PZA BL80</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10003435</t>
+  </si>
+  <si>
+    <t>SUPERMI AYAM BWG 75G</t>
+  </si>
+  <si>
+    <t>10015954</t>
+  </si>
+  <si>
+    <t>GAGA 100 JALAPENO 75</t>
+  </si>
+  <si>
+    <t>20085444</t>
+  </si>
+  <si>
+    <t>GAGA 100 GR.JLPNO 85</t>
+  </si>
+  <si>
+    <t>10000713</t>
+  </si>
+  <si>
+    <t>INDOMI KLD AYAM 75G</t>
+  </si>
+  <si>
+    <t>10002560</t>
+  </si>
+  <si>
+    <t>INDOMI SOTO MIE 70GR</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20007834</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO SPCL 75</t>
+  </si>
+  <si>
+    <t>20085462</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO LMNG 80</t>
+  </si>
+  <si>
+    <t>20137101</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO PD.D 76</t>
+  </si>
+  <si>
+    <t>20137102</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO KN 76G</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10000652</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM BWNG 69G</t>
+  </si>
+  <si>
+    <t>10000184</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM SPECL68G</t>
+  </si>
+  <si>
+    <t>10035954</t>
+  </si>
+  <si>
+    <t>INDOMIE EMPL/GTNG 75</t>
+  </si>
+  <si>
+    <t>10035955</t>
+  </si>
+  <si>
+    <t>INDOMIE MI KOCOK 75G</t>
+  </si>
+  <si>
+    <t>20085115</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG ACEH 90G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20074112</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RICA 85G</t>
+  </si>
+  <si>
+    <t>20044199</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG CB.IJO85</t>
+  </si>
+  <si>
+    <t>20138358</t>
+  </si>
+  <si>
+    <t>INDOMI NYEMK B/LDS80</t>
+  </si>
+  <si>
+    <t>20140632</t>
+  </si>
+  <si>
+    <t>INDOMI NYMEK J/RD 84</t>
+  </si>
+  <si>
+    <t>20133372</t>
+  </si>
+  <si>
+    <t>INDOMIE RWN MERCON75</t>
+  </si>
+  <si>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20019930</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDANG91</t>
+  </si>
+  <si>
+    <t>20128381</t>
+  </si>
+  <si>
+    <t>INDOMI TRI MSO RMN86</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20132338</t>
+  </si>
+  <si>
+    <t>INDOMIE TORI KARA 89</t>
+  </si>
+  <si>
+    <t>20135989</t>
+  </si>
+  <si>
+    <t>INDOMI SPCY RMYEON83</t>
+  </si>
+  <si>
+    <t>20135990</t>
+  </si>
+  <si>
+    <t>INDOMI FIERY CHKIN94</t>
+  </si>
+  <si>
+    <t>20136533</t>
+  </si>
+  <si>
+    <t>INDOMIE K-ROSE 85G</t>
+  </si>
+  <si>
+    <t>20101747</t>
+  </si>
+  <si>
+    <t>INDOMI SBLAK HOT/J75</t>
+  </si>
+  <si>
+    <t>20093221</t>
+  </si>
+  <si>
+    <t>INDOMIE GR AYM.GP 85</t>
+  </si>
+  <si>
+    <t>20032100</t>
+  </si>
+  <si>
+    <t>INDOMIE KRT/AYM PG90</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20032099</t>
+  </si>
+  <si>
+    <t>INDOMIE KRT/GR.SPC90</t>
+  </si>
+  <si>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR SP JUMB129</t>
+  </si>
+  <si>
+    <t>10003801</t>
+  </si>
+  <si>
+    <t>INDOMI JMB AYM PG127</t>
+  </si>
+  <si>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDNG120</t>
+  </si>
+  <si>
+    <t>20142599</t>
+  </si>
+  <si>
+    <t>INDOMI GR CB.IJO 120</t>
+  </si>
+  <si>
+    <t>20085013</t>
+  </si>
+  <si>
+    <t>BD MIE URAI ORG 140G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>10000507</t>
+  </si>
+  <si>
+    <t>A/B MIE TELOR 200GR</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004055</t>
+  </si>
+  <si>
+    <t>3AYAM MIE TLR MRH200</t>
+  </si>
+  <si>
+    <t>10004262</t>
+  </si>
+  <si>
+    <t>3AYAM MIE TLR KNG200</t>
+  </si>
+  <si>
+    <t>10037027</t>
+  </si>
+  <si>
+    <t>AAA BIHUN 220GR</t>
+  </si>
+  <si>
+    <t>20043409</t>
+  </si>
+  <si>
+    <t>IDM BIHUN BERAS 220G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20034699</t>
+  </si>
+  <si>
+    <t>BIHUN JAGUNG 320G</t>
+  </si>
+  <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138950</t>
+  </si>
+  <si>
+    <t>IDM ABON AYAM 80G</t>
+  </si>
+  <si>
+    <t>10000245</t>
+  </si>
+  <si>
+    <t>RATU ABON SAPI 90G</t>
+  </si>
+  <si>
+    <t>20140909</t>
+  </si>
+  <si>
+    <t>B.FARM TERI KB 60G</t>
+  </si>
+  <si>
+    <t>20020770</t>
+  </si>
+  <si>
+    <t>MERBABU KR.BAWANG200</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20112822</t>
+  </si>
+  <si>
+    <t>MIGELAS AYAM BWG 6'S</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20094642</t>
+  </si>
+  <si>
+    <t>MIGELAS SOTO AYAM 6S</t>
+  </si>
+  <si>
+    <t>20032996</t>
+  </si>
+  <si>
+    <t>PALDO HOT&amp;SPICY 120</t>
+  </si>
+  <si>
+    <t>20138114</t>
+  </si>
+  <si>
+    <t>PALDO BIBMEN II 130G</t>
+  </si>
+  <si>
     <t>20099679</t>
   </si>
   <si>
@@ -214,420 +640,6 @@
     <t>LEMONILO PDS KOREA68</t>
   </si>
   <si>
-    <t>20132986</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI TRYKI120</t>
-  </si>
-  <si>
-    <t>20094693</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI AYM 5.5K</t>
-  </si>
-  <si>
-    <t>20119164</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI YKNKU115</t>
-  </si>
-  <si>
-    <t>20143284</t>
-  </si>
-  <si>
-    <t>WOWSPAGETIGORENG79G</t>
-  </si>
-  <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI CARB80</t>
-  </si>
-  <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI BOLOG76</t>
-  </si>
-  <si>
-    <t>20137860</t>
-  </si>
-  <si>
-    <t>WOW AGLI OLIO 75G</t>
-  </si>
-  <si>
-    <t>20138738</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI CRBO 80G</t>
-  </si>
-  <si>
-    <t>20138739</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI BGLN 84G</t>
-  </si>
-  <si>
-    <t>20140633</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG SPC 5S</t>
-  </si>
-  <si>
-    <t>20140657</t>
-  </si>
-  <si>
-    <t>INDOMIE AYAM BWG 5S</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10003435</t>
-  </si>
-  <si>
-    <t>SUPERMI AYAM BWG 75G</t>
-  </si>
-  <si>
-    <t>10015954</t>
-  </si>
-  <si>
-    <t>GAGA 100 JALAPENO 75</t>
-  </si>
-  <si>
-    <t>20085444</t>
-  </si>
-  <si>
-    <t>GAGA 100 GR.JLPNO 85</t>
-  </si>
-  <si>
-    <t>10000713</t>
-  </si>
-  <si>
-    <t>INDOMI KLD AYAM 75G</t>
-  </si>
-  <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20007834</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO SPCL 75</t>
-  </si>
-  <si>
-    <t>20085462</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO LMNG 80</t>
-  </si>
-  <si>
-    <t>20137101</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO PD.D 76</t>
-  </si>
-  <si>
-    <t>20137102</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO KN 76G</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10000652</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM BWNG 69G</t>
-  </si>
-  <si>
-    <t>10000184</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM SPECL68G</t>
-  </si>
-  <si>
-    <t>10035954</t>
-  </si>
-  <si>
-    <t>INDOMIE EMPL/GTNG 75</t>
-  </si>
-  <si>
-    <t>10035955</t>
-  </si>
-  <si>
-    <t>INDOMIE MI KOCOK 75G</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACEH 90G</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20074112</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RICA 85G</t>
-  </si>
-  <si>
-    <t>20044199</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG CB.IJO85</t>
-  </si>
-  <si>
-    <t>20138358</t>
-  </si>
-  <si>
-    <t>INDOMI NYEMK B/LDS80</t>
-  </si>
-  <si>
-    <t>20140632</t>
-  </si>
-  <si>
-    <t>INDOMI NYMEK J/RD 84</t>
-  </si>
-  <si>
-    <t>20133372</t>
-  </si>
-  <si>
-    <t>INDOMIE RWN MERCON75</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDANG91</t>
-  </si>
-  <si>
-    <t>20128381</t>
-  </si>
-  <si>
-    <t>INDOMI TRI MSO RMN86</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20132338</t>
-  </si>
-  <si>
-    <t>INDOMIE TORI KARA 89</t>
-  </si>
-  <si>
-    <t>20135989</t>
-  </si>
-  <si>
-    <t>INDOMI SPCY RMYEON83</t>
-  </si>
-  <si>
-    <t>20135990</t>
-  </si>
-  <si>
-    <t>INDOMI FIERY CHKIN94</t>
-  </si>
-  <si>
-    <t>20136533</t>
-  </si>
-  <si>
-    <t>INDOMIE K-ROSE 85G</t>
-  </si>
-  <si>
-    <t>20101747</t>
-  </si>
-  <si>
-    <t>INDOMI SBLAK HOT/J75</t>
-  </si>
-  <si>
-    <t>20093221</t>
-  </si>
-  <si>
-    <t>INDOMIE GR AYM.GP 85</t>
-  </si>
-  <si>
-    <t>20032100</t>
-  </si>
-  <si>
-    <t>INDOMIE KRT/AYM PG90</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20032099</t>
-  </si>
-  <si>
-    <t>INDOMIE KRT/GR.SPC90</t>
-  </si>
-  <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
-  </si>
-  <si>
-    <t>10003801</t>
-  </si>
-  <si>
-    <t>INDOMI JMB AYM PG127</t>
-  </si>
-  <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
-  </si>
-  <si>
-    <t>20142599</t>
-  </si>
-  <si>
-    <t>INDOMI GR CB.IJO 120</t>
-  </si>
-  <si>
-    <t>20085013</t>
-  </si>
-  <si>
-    <t>BD MIE URAI ORG 140G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>10000507</t>
-  </si>
-  <si>
-    <t>A/B MIE TELOR 200GR</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004055</t>
-  </si>
-  <si>
-    <t>3AYAM MIE TLR MRH200</t>
-  </si>
-  <si>
-    <t>10004262</t>
-  </si>
-  <si>
-    <t>3AYAM MIE TLR KNG200</t>
-  </si>
-  <si>
-    <t>10037027</t>
-  </si>
-  <si>
-    <t>AAA BIHUN 220GR</t>
-  </si>
-  <si>
-    <t>20043409</t>
-  </si>
-  <si>
-    <t>IDM BIHUN BERAS 220G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20034699</t>
-  </si>
-  <si>
-    <t>BIHUN JAGUNG 320G</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
-  </si>
-  <si>
-    <t>10000245</t>
-  </si>
-  <si>
-    <t>RATU ABON SAPI 90G</t>
-  </si>
-  <si>
-    <t>20140909</t>
-  </si>
-  <si>
-    <t>B.FARM TERI KB 60G</t>
-  </si>
-  <si>
-    <t>20020770</t>
-  </si>
-  <si>
-    <t>MERBABU KR.BAWANG200</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20112822</t>
-  </si>
-  <si>
-    <t>MIGELAS AYAM BWG 6'S</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20094642</t>
-  </si>
-  <si>
-    <t>MIGELAS SOTO AYAM 6S</t>
-  </si>
-  <si>
-    <t>20032996</t>
-  </si>
-  <si>
-    <t>PALDO HOT&amp;SPICY 120</t>
-  </si>
-  <si>
-    <t>20138114</t>
-  </si>
-  <si>
-    <t>PALDO BIBMEN II 130G</t>
-  </si>
-  <si>
     <t>20127764</t>
   </si>
   <si>
@@ -877,16 +889,16 @@
     <t>SEDAAP MIE K/S CUP81</t>
   </si>
   <si>
+    <t>20130519</t>
+  </si>
+  <si>
+    <t>SDP MI AYM NMPOL 75G</t>
+  </si>
+  <si>
     <t>20113844</t>
   </si>
   <si>
     <t>SEDAAP MI AYM JRT 75</t>
-  </si>
-  <si>
-    <t>20130519</t>
-  </si>
-  <si>
-    <t>SDP MI AYM NMPOL 75G</t>
   </si>
   <si>
     <t>20122255</t>
@@ -1480,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2065,7 +2077,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>19</v>
@@ -2085,7 +2097,7 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>19</v>
@@ -2105,10 +2117,10 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2125,10 +2137,10 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3322,10 +3334,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>19</v>
@@ -3333,19 +3345,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>19</v>
@@ -3353,19 +3365,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>19</v>
@@ -3382,10 +3394,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>19</v>
@@ -3402,13 +3414,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3422,13 +3434,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3442,13 +3454,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3462,30 +3474,30 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3493,19 +3505,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3522,10 +3534,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3542,10 +3554,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>19</v>
@@ -3553,19 +3565,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>19</v>
@@ -3573,22 +3585,22 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3602,13 +3614,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3622,13 +3634,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3642,13 +3654,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3662,10 +3674,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3673,19 +3685,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3693,19 +3705,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3722,10 +3734,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3742,10 +3754,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3762,10 +3774,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -3782,10 +3794,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -3802,10 +3814,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3813,19 +3825,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3833,19 +3845,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
@@ -3862,10 +3874,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>19</v>
@@ -3882,13 +3894,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3902,53 +3914,53 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3962,13 +3974,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3982,13 +3994,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4002,13 +4014,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4022,10 +4034,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4042,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4053,19 +4065,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4073,19 +4085,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4102,10 +4114,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4122,10 +4134,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>19</v>
@@ -4142,10 +4154,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>19</v>
@@ -4162,13 +4174,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,13 +4194,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4202,10 +4214,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>171</v>
@@ -4222,50 +4234,50 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>19</v>
@@ -4282,10 +4294,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>19</v>
@@ -4302,50 +4314,50 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4362,10 +4374,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4382,10 +4394,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4402,10 +4414,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4422,10 +4434,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4442,10 +4454,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4453,19 +4465,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4473,19 +4485,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4502,10 +4514,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4522,10 +4534,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4542,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4553,19 +4565,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4573,19 +4585,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>6</v>
@@ -4602,10 +4614,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>6</v>
@@ -4622,53 +4634,53 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>186</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4682,10 +4694,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>186</v>
@@ -4702,13 +4714,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4722,12 +4734,52 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E162" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F162" s="1" t="s">
+      <c r="F164" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
   <si>
     <t/>
   </si>
@@ -220,18 +220,6 @@
     <t>TASTY BAKMI YKNKU115</t>
   </si>
   <si>
-    <t>20140633</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG SPC 5S</t>
-  </si>
-  <si>
-    <t>20140657</t>
-  </si>
-  <si>
-    <t>INDOMIE AYAM BWG 5S</t>
-  </si>
-  <si>
     <t>20143284</t>
   </si>
   <si>
@@ -614,18 +602,6 @@
   </si>
   <si>
     <t>MIGELAS SOTO AYAM 6S</t>
-  </si>
-  <si>
-    <t>20032996</t>
-  </si>
-  <si>
-    <t>PALDO HOT&amp;SPICY 120</t>
-  </si>
-  <si>
-    <t>20138114</t>
-  </si>
-  <si>
-    <t>PALDO BIBMEN II 130G</t>
   </si>
   <si>
     <t>20099679</t>
@@ -1492,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2114,13 +2090,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2134,13 +2110,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2157,7 +2133,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>19</v>
@@ -2177,7 +2153,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>19</v>
@@ -2197,10 +2173,10 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2217,10 +2193,10 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2237,7 +2213,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2257,7 +2233,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2265,19 +2241,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2285,19 +2261,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2314,10 +2290,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2334,10 +2310,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2354,10 +2330,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2365,19 +2341,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2385,19 +2361,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2414,10 +2390,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2434,10 +2410,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2454,10 +2430,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2465,19 +2441,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2485,19 +2461,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2514,10 +2490,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2534,10 +2510,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2554,10 +2530,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2565,19 +2541,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2585,19 +2561,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2614,10 +2590,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2634,10 +2610,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2654,10 +2630,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2674,10 +2650,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -2685,19 +2661,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -2705,16 +2681,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>4</v>
@@ -2725,16 +2701,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>18</v>
@@ -2745,19 +2721,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -2774,10 +2750,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2794,10 +2770,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2814,10 +2790,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2834,10 +2810,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2854,10 +2830,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -2865,19 +2841,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2885,19 +2861,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -2914,10 +2890,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -2934,10 +2910,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -2954,10 +2930,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -2974,73 +2950,73 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3054,13 +3030,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3074,93 +3050,93 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="E82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3174,13 +3150,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>186</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3194,30 +3170,30 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>19</v>
@@ -3225,39 +3201,39 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>195</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>19</v>
@@ -3274,13 +3250,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3294,50 +3270,50 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>19</v>
@@ -3345,19 +3321,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>19</v>
@@ -3365,22 +3341,22 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3394,13 +3370,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3414,10 +3390,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>19</v>
@@ -3434,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>19</v>
@@ -3445,59 +3421,59 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3505,19 +3481,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3525,19 +3501,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3545,59 +3521,59 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>19</v>
@@ -3614,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>19</v>
@@ -3634,50 +3610,50 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3685,19 +3661,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3705,19 +3681,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3734,10 +3710,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3754,10 +3730,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3774,10 +3750,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -3785,19 +3761,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -3805,19 +3781,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3825,19 +3801,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3845,22 +3821,22 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3874,70 +3850,70 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -3945,22 +3921,22 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3974,13 +3950,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3994,13 +3970,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4014,30 +3990,30 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4045,19 +4021,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4065,19 +4041,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4085,19 +4061,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4114,10 +4090,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4134,13 +4110,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4154,13 +4130,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4174,13 +4150,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4194,10 +4170,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>19</v>
@@ -4205,159 +4181,159 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4374,10 +4350,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4394,10 +4370,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4414,10 +4390,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4425,19 +4401,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4445,19 +4421,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4465,19 +4441,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4485,19 +4461,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4514,10 +4490,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4525,19 +4501,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4545,19 +4521,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4565,19 +4541,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4585,99 +4561,99 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>19</v>
@@ -4694,92 +4670,12 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F164" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="360">
   <si>
     <t/>
   </si>
@@ -661,15 +661,27 @@
     <t>WONHAE TPOKI CARB 80</t>
   </si>
   <si>
+    <t>20135130</t>
+  </si>
+  <si>
+    <t>NISSIN SLTD.EGG 117G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20135131</t>
+  </si>
+  <si>
+    <t>NISSIN SPC S.EGG 117</t>
+  </si>
+  <si>
     <t>20019479</t>
   </si>
   <si>
     <t>N/SHIM SPCY MUSHR120</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>20115156</t>
   </si>
   <si>
@@ -682,72 +694,60 @@
     <t>MJGAE SPCY RPKI 155G</t>
   </si>
   <si>
+    <t>20096499</t>
+  </si>
+  <si>
+    <t>SMYANG AYM CRBO 130G</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20052583</t>
+  </si>
+  <si>
+    <t>SMYANG GR PDS AYM140</t>
+  </si>
+  <si>
+    <t>20127820</t>
+  </si>
+  <si>
+    <t>SMYANG CRM CBNARA140</t>
+  </si>
+  <si>
+    <t>20112749</t>
+  </si>
+  <si>
+    <t>SAMYANG SPICY 120G</t>
+  </si>
+  <si>
+    <t>20138572</t>
+  </si>
+  <si>
+    <t>SAMYANG ROSE 140G</t>
+  </si>
+  <si>
+    <t>20139702</t>
+  </si>
+  <si>
+    <t>SMYANG QTR.CHSE 145G</t>
+  </si>
+  <si>
     <t>20117989</t>
   </si>
   <si>
     <t>M/S TOPOKKI ORI 132G</t>
   </si>
   <si>
-    <t>20096499</t>
-  </si>
-  <si>
-    <t>SMYANG AYM CRBO 130G</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20052583</t>
-  </si>
-  <si>
-    <t>SMYANG GR PDS AYM140</t>
-  </si>
-  <si>
-    <t>20127820</t>
-  </si>
-  <si>
-    <t>SMYANG CRM CBNARA140</t>
-  </si>
-  <si>
-    <t>20112749</t>
-  </si>
-  <si>
-    <t>SAMYANG SPICY 120G</t>
-  </si>
-  <si>
-    <t>20138572</t>
-  </si>
-  <si>
-    <t>SAMYANG ROSE 140G</t>
-  </si>
-  <si>
-    <t>20139702</t>
-  </si>
-  <si>
-    <t>SMYANG QTR.CHSE 145G</t>
-  </si>
-  <si>
-    <t>20135130</t>
-  </si>
-  <si>
-    <t>NISSIN SLTD.EGG 117G</t>
+    <t>20031775</t>
+  </si>
+  <si>
+    <t>NISSIN GEKIKARA 109G</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>20135131</t>
-  </si>
-  <si>
-    <t>NISSIN SPC S.EGG 117</t>
-  </si>
-  <si>
-    <t>20031775</t>
-  </si>
-  <si>
-    <t>NISSIN GEKIKARA 109G</t>
-  </si>
-  <si>
     <t>20067395</t>
   </si>
   <si>
@@ -770,6 +770,21 @@
   </si>
   <si>
     <t>RMN YES HKTA CHKN88G</t>
+  </si>
+  <si>
+    <t>20143800</t>
+  </si>
+  <si>
+    <t>CNCMN C/RMN KJ PDS75</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20143801</t>
+  </si>
+  <si>
+    <t>CNCMN C/RMN EX PDS75</t>
   </si>
   <si>
     <t>20039494</t>
@@ -1468,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3413,7 +3428,7 @@
         <v>218</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>19</v>
@@ -3433,7 +3448,7 @@
         <v>218</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>19</v>
@@ -3453,7 +3468,7 @@
         <v>218</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>19</v>
@@ -3473,7 +3488,7 @@
         <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3490,10 +3505,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3501,19 +3516,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3530,13 +3545,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3550,10 +3565,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3570,13 +3585,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3590,10 +3605,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>19</v>
@@ -3610,10 +3625,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>19</v>
@@ -3621,19 +3636,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>19</v>
@@ -3641,19 +3656,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3670,10 +3685,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3690,10 +3705,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3710,10 +3725,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3730,10 +3745,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3750,13 +3765,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3770,13 +3785,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3790,10 +3805,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3801,19 +3816,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3821,42 +3836,42 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3870,13 +3885,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3890,90 +3905,90 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>19</v>
@@ -3981,19 +3996,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>19</v>
@@ -4010,10 +4025,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4030,10 +4045,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4041,19 +4056,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4061,19 +4076,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4081,19 +4096,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4101,59 +4116,59 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>167</v>
@@ -4161,22 +4176,22 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4190,13 +4205,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4210,10 +4225,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4221,19 +4236,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>19</v>
@@ -4241,22 +4256,22 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4270,13 +4285,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4290,10 +4305,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4301,19 +4316,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E142" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4321,19 +4336,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4341,19 +4356,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4361,19 +4376,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4381,19 +4396,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4410,10 +4425,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4430,10 +4445,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4441,19 +4456,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4461,19 +4476,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4481,19 +4496,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4510,10 +4525,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4530,10 +4545,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4541,19 +4556,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4561,22 +4576,22 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4590,13 +4605,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>182</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4610,30 +4625,30 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>182</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>182</v>
@@ -4641,41 +4656,81 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F160" s="1" t="s">
+      <c r="F162" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="352">
   <si>
     <t/>
   </si>
@@ -115,19 +115,19 @@
     <t>20096589</t>
   </si>
   <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
+    <t>SEDAAP MI GRG 5X91 G</t>
   </si>
   <si>
     <t>20096590</t>
   </si>
   <si>
-    <t>SEDAAP MIE SOTO 5'S</t>
+    <t>SEDAAP MI STO 5x76 G</t>
   </si>
   <si>
     <t>20140674</t>
   </si>
   <si>
-    <t>SEDAAP AYM BWG 5'S</t>
+    <t>SEDAAP MI AYB 5x71 G</t>
   </si>
   <si>
     <t>10023790</t>
@@ -535,15 +535,6 @@
     <t>AAA BIHUN 220GR</t>
   </si>
   <si>
-    <t>20043409</t>
-  </si>
-  <si>
-    <t>IDM BIHUN BERAS 220G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
     <t>20034699</t>
   </si>
   <si>
@@ -619,7 +610,7 @@
     <t>20127764</t>
   </si>
   <si>
-    <t>N/SHIM STIR FRY 131</t>
+    <t>N/SHIM STR FRY 131 G</t>
   </si>
   <si>
     <t>18</t>
@@ -679,7 +670,7 @@
     <t>20019479</t>
   </si>
   <si>
-    <t>N/SHIM SPCY MUSHR120</t>
+    <t>N/SHIM SPCY M 120 G</t>
   </si>
   <si>
     <t>20115156</t>
@@ -697,7 +688,7 @@
     <t>20096499</t>
   </si>
   <si>
-    <t>SMYANG AYM CRBO 130G</t>
+    <t>SMYANG AYM CRB 130 G</t>
   </si>
   <si>
     <t>20</t>
@@ -778,9 +769,6 @@
     <t>CNCMN C/RMN KJ PDS75</t>
   </si>
   <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
     <t>20143801</t>
   </si>
   <si>
@@ -851,18 +839,6 @@
   </si>
   <si>
     <t>SUPER BUBUR KARI 46G</t>
-  </si>
-  <si>
-    <t>20140905</t>
-  </si>
-  <si>
-    <t>NASINDO NASI GR. 85G</t>
-  </si>
-  <si>
-    <t>20140904</t>
-  </si>
-  <si>
-    <t>NASINDO SOTO 65G</t>
   </si>
   <si>
     <t>20045610</t>
@@ -1483,7 +1459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3068,110 +3044,110 @@
         <v>164</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>176</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>6</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>182</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3185,13 +3161,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3205,50 +3181,50 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>19</v>
@@ -3256,19 +3232,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>19</v>
@@ -3285,10 +3261,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>19</v>
@@ -3296,19 +3272,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>19</v>
@@ -3316,19 +3292,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>19</v>
@@ -3336,39 +3312,39 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -3376,39 +3352,39 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>19</v>
@@ -3425,10 +3401,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>19</v>
@@ -3436,19 +3412,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>19</v>
@@ -3456,19 +3432,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>19</v>
@@ -3476,19 +3452,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3496,19 +3472,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3525,10 +3501,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3536,39 +3512,39 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3576,39 +3552,39 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>19</v>
@@ -3616,19 +3592,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>19</v>
@@ -3636,19 +3612,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>19</v>
@@ -3665,10 +3641,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3676,19 +3652,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3696,19 +3672,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3716,19 +3692,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3736,19 +3712,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3756,59 +3732,59 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>255</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>255</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3816,19 +3792,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3836,19 +3812,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
@@ -3856,39 +3832,39 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3896,39 +3872,39 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>167</v>
@@ -3936,59 +3912,59 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>19</v>
@@ -3996,19 +3972,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>19</v>
@@ -4016,19 +3992,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4036,19 +4012,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4056,19 +4032,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4076,19 +4052,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4096,139 +4072,139 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4236,79 +4212,79 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4316,19 +4292,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4336,19 +4312,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4356,19 +4332,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4376,19 +4352,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4396,19 +4372,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4416,19 +4392,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4436,19 +4412,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4456,19 +4432,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4476,19 +4452,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4496,19 +4472,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4516,19 +4492,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4536,19 +4512,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4556,181 +4532,121 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>6</v>
+        <v>179</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>6</v>
+        <v>179</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>182</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F162" s="1" t="s">
         <v>19</v>
       </c>
     </row>
